--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="411">
   <si>
     <t/>
   </si>
@@ -145,13 +145,34 @@
     <t>RT,(E-6B)</t>
   </si>
   <si>
+    <t>20011308</t>
+  </si>
+  <si>
+    <t>KALPANAX K CREAM 5GR</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20094802</t>
+  </si>
+  <si>
+    <t>88 KRIM ANTI JAMUR 5</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>RT,(E-7B)</t>
+  </si>
+  <si>
     <t>10000549</t>
   </si>
   <si>
     <t>COUNTERPAIN CREAM 30</t>
   </si>
   <si>
-    <t>13</t>
+    <t>15</t>
   </si>
   <si>
     <t>20047965</t>
@@ -160,7 +181,7 @@
     <t>HOT IN CREAM 120ML</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>20057841</t>
@@ -169,7 +190,7 @@
     <t>HOT IN CREAM 60G</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>20080244</t>
@@ -178,7 +199,7 @@
     <t>HOT IN CRM STRNG 120</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
   </si>
   <si>
     <t>20019446</t>
@@ -187,7 +208,7 @@
     <t>C/LANG MINYAK GPU 60</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>20054951</t>
@@ -394,9 +415,6 @@
     <t>INSTO COOL 7.5ML</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20129405</t>
   </si>
   <si>
@@ -619,9 +637,6 @@
     <t>C/KAPAK MNYK ANGIN10</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>20054022</t>
   </si>
   <si>
@@ -697,9 +712,6 @@
     <t>BODREX SKT KEPALA 20</t>
   </si>
   <si>
-    <t>RT,(E-7B)</t>
-  </si>
-  <si>
     <t>10040122</t>
   </si>
   <si>
@@ -874,67 +886,103 @@
     <t>H/PLAST KAIN FUN10'S</t>
   </si>
   <si>
+    <t>10000665</t>
+  </si>
+  <si>
+    <t>MYLANTA OBAT MAAG 10</t>
+  </si>
+  <si>
+    <t>10003995</t>
+  </si>
+  <si>
+    <t>HEMAVITON ACTION 5'S</t>
+  </si>
+  <si>
+    <t>20137316</t>
+  </si>
+  <si>
+    <t>HNSPLST  TRANSP 10'S</t>
+  </si>
+  <si>
+    <t>20137414</t>
+  </si>
+  <si>
+    <t>DOLO NEUROBION 10S</t>
+  </si>
+  <si>
+    <t>TG,(E-4B)</t>
+  </si>
+  <si>
+    <t>20141957</t>
+  </si>
+  <si>
+    <t>ULTRA FLU STR 10S</t>
+  </si>
+  <si>
     <t>10000075</t>
   </si>
   <si>
     <t>KONIDIN OBAT BTK 4'S</t>
   </si>
   <si>
-    <t>10000665</t>
-  </si>
-  <si>
-    <t>MYLANTA OBAT MAAG 10</t>
-  </si>
-  <si>
-    <t>10003995</t>
-  </si>
-  <si>
-    <t>HEMAVITON ACTION 5'S</t>
-  </si>
-  <si>
-    <t>20137316</t>
-  </si>
-  <si>
-    <t>HNSPLST  TRANSP 10'S</t>
-  </si>
-  <si>
-    <t>20137414</t>
-  </si>
-  <si>
-    <t>DOLO NEUROBION 10S</t>
-  </si>
-  <si>
-    <t>TG,(E-4B)</t>
-  </si>
-  <si>
     <t>10010246</t>
   </si>
   <si>
     <t>NEUROBION VIT.10'S</t>
   </si>
   <si>
+    <t>20027551</t>
+  </si>
+  <si>
+    <t>HOLSTICARE ESTR C 4S</t>
+  </si>
+  <si>
+    <t>20120361</t>
+  </si>
+  <si>
+    <t>ENTROSTOP STR 10'S</t>
+  </si>
+  <si>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
+  </si>
+  <si>
     <t>10030867</t>
   </si>
   <si>
     <t>PROCOLD OBAT FLU 6'S</t>
   </si>
   <si>
-    <t>20027551</t>
-  </si>
-  <si>
-    <t>HOLSTICARE ESTR C 4S</t>
-  </si>
-  <si>
-    <t>20120361</t>
-  </si>
-  <si>
-    <t>ENTROSTOP STR 10'S</t>
-  </si>
-  <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
+    <t>20053803</t>
+  </si>
+  <si>
+    <t>NEUROBION FORTE 10'S</t>
+  </si>
+  <si>
+    <t>20056311</t>
+  </si>
+  <si>
+    <t>CEREBRF.GUMMY STR20G</t>
+  </si>
+  <si>
+    <t>20087096</t>
+  </si>
+  <si>
+    <t>IM-BOOST TABLET 4'S</t>
+  </si>
+  <si>
+    <t>20090384</t>
+  </si>
+  <si>
+    <t>DIAPET KAPSUL 10'S</t>
+  </si>
+  <si>
+    <t>10003650</t>
+  </si>
+  <si>
+    <t>ENERVON C TABLET 4'S</t>
   </si>
   <si>
     <t>20010358</t>
@@ -943,28 +991,16 @@
     <t>MXAGRIP FLU&amp;BATUK 4S</t>
   </si>
   <si>
-    <t>20053803</t>
-  </si>
-  <si>
-    <t>NEUROBION FORTE 10'S</t>
-  </si>
-  <si>
-    <t>20056311</t>
-  </si>
-  <si>
-    <t>CEREBRF.GUMMY STR20G</t>
-  </si>
-  <si>
-    <t>20087096</t>
-  </si>
-  <si>
-    <t>IM-BOOST TABLET 4'S</t>
-  </si>
-  <si>
-    <t>20090384</t>
-  </si>
-  <si>
-    <t>DIAPET KAPSUL 10'S</t>
+    <t>20090383</t>
+  </si>
+  <si>
+    <t>LAXING STR 10'S</t>
+  </si>
+  <si>
+    <t>20102471</t>
+  </si>
+  <si>
+    <t>CDR VITAMIN C 2'S</t>
   </si>
   <si>
     <t>10000069</t>
@@ -973,64 +1009,58 @@
     <t>MIXAGRIP O.SKT FLU4S</t>
   </si>
   <si>
-    <t>10003650</t>
-  </si>
-  <si>
-    <t>ENERVON C TABLET 4'S</t>
-  </si>
-  <si>
-    <t>20090383</t>
-  </si>
-  <si>
-    <t>LAXING STR 10'S</t>
-  </si>
-  <si>
-    <t>20102471</t>
-  </si>
-  <si>
-    <t>CDR VITAMIN C 2'S</t>
-  </si>
-  <si>
     <t>20014241</t>
   </si>
   <si>
     <t>AMBEVEN U/ WASR 10'S</t>
   </si>
   <si>
+    <t>20124298</t>
+  </si>
+  <si>
+    <t>IM-BOOST BONE ORG 2S</t>
+  </si>
+  <si>
+    <t>20048747</t>
+  </si>
+  <si>
+    <t>MICROLAX GEL 5ML</t>
+  </si>
+  <si>
     <t>20057705</t>
   </si>
   <si>
     <t>KONIDIN OBAT BTK 5X7</t>
   </si>
   <si>
-    <t>20124298</t>
-  </si>
-  <si>
-    <t>IM-BOOST BONE ORG 2S</t>
-  </si>
-  <si>
-    <t>20048747</t>
-  </si>
-  <si>
-    <t>MICROLAX GEL 5ML</t>
-  </si>
-  <si>
     <t>20083486</t>
   </si>
   <si>
     <t>REDOXON JERUK 2'S</t>
   </si>
   <si>
+    <t>10000197</t>
+  </si>
+  <si>
+    <t>VITACIMIN STRIP 2'S</t>
+  </si>
+  <si>
+    <t>20132440</t>
+  </si>
+  <si>
+    <t>ULTRA CAP GOLD VIT4S</t>
+  </si>
+  <si>
     <t>20140912</t>
   </si>
   <si>
     <t>SM TOLAK ANGIN 15ML</t>
   </si>
   <si>
-    <t>10000197</t>
-  </si>
-  <si>
-    <t>VITACIMIN STRIP 2'S</t>
+    <t>10003980</t>
+  </si>
+  <si>
+    <t>VICEE VIT C LEMON 2S</t>
   </si>
   <si>
     <t>20124837</t>
@@ -1039,16 +1069,10 @@
     <t>KALPANAX SALEP 6G</t>
   </si>
   <si>
-    <t>20132440</t>
-  </si>
-  <si>
-    <t>ULTRA CAP GOLD VIT4S</t>
-  </si>
-  <si>
-    <t>10003980</t>
-  </si>
-  <si>
-    <t>VICEE VIT C LEMON 2S</t>
+    <t>10002862</t>
+  </si>
+  <si>
+    <t>XON-CE VIT.C500MG2'S</t>
   </si>
   <si>
     <t>10037415</t>
@@ -1058,24 +1082,6 @@
   </si>
   <si>
     <t>RT,(E-13B)</t>
-  </si>
-  <si>
-    <t>10002862</t>
-  </si>
-  <si>
-    <t>XON-CE VIT.C500MG2'S</t>
-  </si>
-  <si>
-    <t>20011308</t>
-  </si>
-  <si>
-    <t>KALPANAX K CREAM 5GR</t>
-  </si>
-  <si>
-    <t>20094802</t>
-  </si>
-  <si>
-    <t>88 KRIM ANTI JAMUR 5</t>
   </si>
   <si>
     <t>20111900</t>
@@ -1630,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1918,7 +1924,7 @@
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1938,15 +1944,15 @@
         <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1955,18 +1961,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1975,7 +1981,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1983,10 +1989,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1995,58 +2001,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2055,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -2063,10 +2069,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2075,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -2083,10 +2089,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2095,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -2103,10 +2109,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2115,18 +2121,18 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2135,18 +2141,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2155,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2163,10 +2169,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2175,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2183,10 +2189,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2195,18 +2201,18 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2215,18 +2221,18 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2235,18 +2241,18 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2255,18 +2261,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2275,18 +2281,18 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2295,58 +2301,58 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2355,18 +2361,18 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2375,7 +2381,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
@@ -2383,10 +2389,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2395,18 +2401,18 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2415,18 +2421,18 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2435,18 +2441,18 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2455,18 +2461,18 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2475,18 +2481,18 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2495,18 +2501,18 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2515,18 +2521,18 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2535,18 +2541,18 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2555,18 +2561,18 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2575,18 +2581,18 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2595,7 +2601,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>20</v>
@@ -2603,10 +2609,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2615,7 +2621,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
@@ -2623,10 +2629,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2635,7 +2641,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
@@ -2643,10 +2649,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2655,7 +2661,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>20</v>
@@ -2663,42 +2669,42 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2715,18 +2721,18 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2735,18 +2741,18 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2755,18 +2761,18 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2775,18 +2781,18 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2795,18 +2801,18 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2815,18 +2821,18 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2835,18 +2841,18 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2855,18 +2861,18 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2875,18 +2881,18 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2895,18 +2901,18 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2915,18 +2921,18 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2935,18 +2941,18 @@
         <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2955,18 +2961,18 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2975,18 +2981,18 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2995,27 +3001,27 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3023,30 +3029,30 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3055,7 +3061,7 @@
         <v>19</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3063,10 +3069,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3075,7 +3081,7 @@
         <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3083,10 +3089,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3095,7 +3101,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3103,10 +3109,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3115,7 +3121,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3123,10 +3129,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3135,7 +3141,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3143,10 +3149,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3155,7 +3161,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3163,10 +3169,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3175,7 +3181,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3183,10 +3189,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3195,7 +3201,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3203,10 +3209,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3215,7 +3221,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3223,10 +3229,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3235,7 +3241,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3243,10 +3249,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3255,18 +3261,18 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3275,18 +3281,18 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3295,18 +3301,18 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3315,18 +3321,18 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3335,18 +3341,18 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3355,7 +3361,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
@@ -3363,10 +3369,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3375,18 +3381,18 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3395,10 +3401,10 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,18 +3421,18 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>208</v>
+        <v>65</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3435,18 +3441,18 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3455,30 +3461,30 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3492,21 +3498,21 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3518,15 +3524,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3538,7 +3544,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>223</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3558,7 +3564,7 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>223</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,7 +3581,7 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>228</v>
@@ -3595,10 +3601,10 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,7 +3624,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,7 +3644,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,7 +3664,7 @@
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,10 +3681,10 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3695,10 +3701,10 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,7 +3724,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>223</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,7 +3744,7 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,7 +3764,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3775,10 +3781,10 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3795,10 +3801,10 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>130</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,7 +3824,7 @@
         <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,7 +3844,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,7 +3881,7 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>20</v>
@@ -3895,10 +3901,10 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,7 +3924,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,7 +3944,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,7 +3964,7 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3975,7 +3981,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>20</v>
@@ -3995,10 +4001,10 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,7 +4024,7 @@
         <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4038,7 +4044,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4058,7 +4064,7 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4075,10 +4081,10 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,10 +4101,10 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>228</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4118,7 +4124,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4138,7 +4144,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4158,7 +4164,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4175,10 +4181,10 @@
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>223</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,10 +4201,10 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4218,7 +4224,7 @@
         <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4238,7 +4244,7 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4258,27 +4264,27 @@
         <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>297</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,10 +4301,10 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4318,7 +4324,7 @@
         <v>33</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4338,7 +4344,7 @@
         <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4358,7 +4364,7 @@
         <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4375,10 +4381,10 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,10 +4401,10 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4418,7 +4424,7 @@
         <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4438,7 +4444,7 @@
         <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4458,7 +4464,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,10 +4481,10 @@
         <v>23</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,10 +4501,10 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4518,7 +4524,7 @@
         <v>39</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4538,7 +4544,7 @@
         <v>39</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,10 +4561,10 @@
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4575,10 +4581,10 @@
         <v>23</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,7 +4604,7 @@
         <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,10 +4621,10 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,10 +4641,10 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4658,7 +4664,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,10 +4681,10 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4695,10 +4701,10 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4718,7 +4724,7 @@
         <v>49</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,10 +4741,10 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,19 +4761,19 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>348</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
@@ -4775,19 +4781,19 @@
         <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
@@ -4795,7 +4801,7 @@
         <v>23</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>12</v>
@@ -4803,11 +4809,11 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
@@ -4815,30 +4821,30 @@
         <v>23</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>228</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4852,13 +4858,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4875,7 +4881,7 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>43</v>
@@ -4895,10 +4901,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>228</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,10 +4941,10 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,7 +4961,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>43</v>
@@ -4975,7 +4981,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>43</v>
@@ -4995,7 +5001,7 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>43</v>
@@ -5015,7 +5021,7 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>43</v>
@@ -5035,10 +5041,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
@@ -5075,10 +5081,10 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,10 +5101,10 @@
         <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,10 +5121,10 @@
         <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>223</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,13 +5138,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,10 +5161,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,10 +5181,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,10 +5201,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5215,10 +5221,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,7 +5241,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>12</v>
@@ -5255,10 +5261,10 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5275,7 +5281,7 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>20</v>
@@ -5295,7 +5301,7 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>20</v>
@@ -5315,7 +5321,7 @@
         <v>29</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>20</v>
@@ -5335,10 +5341,10 @@
         <v>29</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,10 +5361,30 @@
         <v>29</v>
       </c>
       <c r="E186" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F186" s="1" t="s">
-        <v>100</v>
+      <c r="F187" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="407">
   <si>
     <t/>
   </si>
@@ -784,12 +784,6 @@
     <t>ANTIMO ANAK JERUK5'S</t>
   </si>
   <si>
-    <t>20138270</t>
-  </si>
-  <si>
-    <t>DETTOL ANTSP PLST 10</t>
-  </si>
-  <si>
     <t>20141639</t>
   </si>
   <si>
@@ -1214,12 +1208,6 @@
   </si>
   <si>
     <t>MY BABY TLN PLS LV60</t>
-  </si>
-  <si>
-    <t>20091604</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLS LP60</t>
   </si>
   <si>
     <t>20040313</t>
@@ -1636,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3901,7 +3889,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>20</v>
@@ -3924,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,7 +3932,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3964,7 +3952,7 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3984,7 +3972,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4001,10 +3989,10 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4044,7 +4032,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4064,7 +4052,7 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4084,7 +4072,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,10 +4089,10 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4144,7 +4132,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4164,7 +4152,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4184,7 +4172,7 @@
         <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,10 +4189,10 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,7 +4212,7 @@
         <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4244,7 +4232,7 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4264,15 +4252,15 @@
         <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4284,7 +4272,7 @@
         <v>29</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>299</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4301,10 +4289,10 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4344,7 +4332,7 @@
         <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,7 +4352,7 @@
         <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4401,10 +4389,10 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4424,7 +4412,7 @@
         <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4444,7 +4432,7 @@
         <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4464,7 +4452,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4501,10 +4489,10 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4524,7 +4512,7 @@
         <v>39</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4544,7 +4532,7 @@
         <v>39</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4564,7 +4552,7 @@
         <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,10 +4569,10 @@
         <v>23</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,7 +4592,7 @@
         <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,7 +4612,7 @@
         <v>42</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4641,10 +4629,10 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4664,7 +4652,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4684,7 +4672,7 @@
         <v>46</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4701,10 +4689,10 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4724,7 +4712,7 @@
         <v>49</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4744,7 +4732,7 @@
         <v>49</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4761,10 +4749,10 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4784,7 +4772,7 @@
         <v>53</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,7 +4789,7 @@
         <v>23</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>12</v>
@@ -4824,15 +4812,15 @@
         <v>56</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>354</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -4841,10 +4829,10 @@
         <v>23</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>356</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,13 +4846,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4881,7 +4869,7 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>43</v>
@@ -4901,10 +4889,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4921,10 +4909,10 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4941,10 +4929,10 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,7 +4949,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>43</v>
@@ -4981,7 +4969,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>43</v>
@@ -5001,7 +4989,7 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>43</v>
@@ -5021,7 +5009,7 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>43</v>
@@ -5041,10 +5029,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5061,7 +5049,7 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
@@ -5081,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5101,10 +5089,10 @@
         <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5121,10 +5109,10 @@
         <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>228</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5138,13 +5126,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>228</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5161,10 +5149,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,10 +5169,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5201,10 +5189,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5221,10 +5209,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5241,7 +5229,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>12</v>
@@ -5261,10 +5249,10 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5281,7 +5269,7 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>20</v>
@@ -5301,7 +5289,7 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>20</v>
@@ -5321,10 +5309,10 @@
         <v>29</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5341,49 +5329,9 @@
         <v>29</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F187" s="1" t="s">
         <v>107</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="406">
   <si>
     <t/>
   </si>
@@ -772,6 +772,12 @@
     <t>PARAMEX SKT KEPALA 4</t>
   </si>
   <si>
+    <t>20065430</t>
+  </si>
+  <si>
+    <t>HNSAPLAST AQUA PRO 6</t>
+  </si>
+  <si>
     <t>20129404</t>
   </si>
   <si>
@@ -808,30 +814,24 @@
     <t>SANGOBION (10'S)</t>
   </si>
   <si>
+    <t>10003514</t>
+  </si>
+  <si>
+    <t>H/PLAST KAIN ELAST10</t>
+  </si>
+  <si>
     <t>20044054</t>
   </si>
   <si>
     <t>C/LANG KOOLFEVER BYI</t>
   </si>
   <si>
-    <t>20065430</t>
-  </si>
-  <si>
-    <t>HNSAPLAST AQUA PRO 6</t>
-  </si>
-  <si>
     <t>10000154</t>
   </si>
   <si>
     <t>NEOZEP FORTE STR.4'S</t>
   </si>
   <si>
-    <t>10003514</t>
-  </si>
-  <si>
-    <t>H/PLAST KAIN ELAST10</t>
-  </si>
-  <si>
     <t>10028800</t>
   </si>
   <si>
@@ -850,6 +850,12 @@
     <t>FATIGON SPIRIT 6'S</t>
   </si>
   <si>
+    <t>20133187</t>
+  </si>
+  <si>
+    <t>H/PLAST KAIN FUN10'S</t>
+  </si>
+  <si>
     <t>10000452</t>
   </si>
   <si>
@@ -874,10 +880,10 @@
     <t>CL KOOL FEVER DEWASA</t>
   </si>
   <si>
-    <t>20133187</t>
-  </si>
-  <si>
-    <t>H/PLAST KAIN FUN10'S</t>
+    <t>20137316</t>
+  </si>
+  <si>
+    <t>HNSPLST  TRANSP 10'S</t>
   </si>
   <si>
     <t>10000665</t>
@@ -892,10 +898,10 @@
     <t>HEMAVITON ACTION 5'S</t>
   </si>
   <si>
-    <t>20137316</t>
-  </si>
-  <si>
-    <t>HNSPLST  TRANSP 10'S</t>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
   </si>
   <si>
     <t>20137414</t>
@@ -904,9 +910,6 @@
     <t>DOLO NEUROBION 10S</t>
   </si>
   <si>
-    <t>TG,(E-4B)</t>
-  </si>
-  <si>
     <t>20141957</t>
   </si>
   <si>
@@ -931,16 +934,22 @@
     <t>HOLSTICARE ESTR C 4S</t>
   </si>
   <si>
+    <t>20087096</t>
+  </si>
+  <si>
+    <t>IM-BOOST TABLET 4'S</t>
+  </si>
+  <si>
     <t>20120361</t>
   </si>
   <si>
     <t>ENTROSTOP STR 10'S</t>
   </si>
   <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
+    <t>10003650</t>
+  </si>
+  <si>
+    <t>ENERVON C TABLET 4'S</t>
   </si>
   <si>
     <t>10030867</t>
@@ -961,22 +970,10 @@
     <t>CEREBRF.GUMMY STR20G</t>
   </si>
   <si>
-    <t>20087096</t>
-  </si>
-  <si>
-    <t>IM-BOOST TABLET 4'S</t>
-  </si>
-  <si>
     <t>20090384</t>
   </si>
   <si>
     <t>DIAPET KAPSUL 10'S</t>
-  </si>
-  <si>
-    <t>10003650</t>
-  </si>
-  <si>
-    <t>ENERVON C TABLET 4'S</t>
   </si>
   <si>
     <t>20010358</t>
@@ -3832,7 +3829,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3852,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3889,7 +3886,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>20</v>
@@ -3912,7 +3909,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,7 +3929,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3952,7 +3949,7 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3972,7 +3969,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3989,7 +3986,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>20</v>
@@ -4089,10 +4086,10 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,7 +4109,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4132,7 +4129,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,7 +4149,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4172,7 +4169,7 @@
         <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4189,7 +4186,7 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>20</v>
@@ -4212,7 +4209,7 @@
         <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4232,7 +4229,7 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4252,15 +4249,15 @@
         <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>297</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4272,16 +4269,16 @@
         <v>29</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
@@ -4289,18 +4286,18 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4317,10 +4314,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4332,15 +4329,15 @@
         <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4352,15 +4349,15 @@
         <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4372,16 +4369,16 @@
         <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
@@ -4389,18 +4386,18 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4412,15 +4409,15 @@
         <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4432,15 +4429,15 @@
         <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4452,15 +4449,15 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4472,16 +4469,16 @@
         <v>36</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
@@ -4489,18 +4486,18 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4517,10 +4514,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4537,10 +4534,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4557,10 +4554,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4577,10 +4574,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4597,10 +4594,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4617,10 +4614,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4637,10 +4634,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4657,10 +4654,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4677,10 +4674,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4697,10 +4694,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4717,10 +4714,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4737,10 +4734,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4757,10 +4754,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4777,10 +4774,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4797,10 +4794,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4812,15 +4809,15 @@
         <v>56</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -4837,10 +4834,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -4857,10 +4854,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -4877,10 +4874,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -4897,10 +4894,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -4917,10 +4914,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -4937,10 +4934,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -4957,10 +4954,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -4977,10 +4974,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -4997,10 +4994,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5017,10 +5014,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5037,10 +5034,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5057,10 +5054,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5077,10 +5074,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5097,10 +5094,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5117,10 +5114,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5137,10 +5134,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5157,10 +5154,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5177,10 +5174,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5197,10 +5194,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5217,10 +5214,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5237,10 +5234,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5257,10 +5254,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5277,10 +5274,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5297,10 +5294,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5317,10 +5314,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="402">
   <si>
     <t/>
   </si>
@@ -685,12 +685,6 @@
     <t>PANADOL CAPLET EXT10</t>
   </si>
   <si>
-    <t>10016198</t>
-  </si>
-  <si>
-    <t>H/PLAST KOYO PNS 10S</t>
-  </si>
-  <si>
     <t>10034123</t>
   </si>
   <si>
@@ -716,12 +710,6 @@
   </si>
   <si>
     <t>HISAMITSU KMPRS BABY</t>
-  </si>
-  <si>
-    <t>20022903</t>
-  </si>
-  <si>
-    <t>H/PLAST KOYO HNGT10S</t>
   </si>
   <si>
     <t>20052425</t>
@@ -1621,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3549,15 +3537,15 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3569,7 +3557,7 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,10 +3574,10 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>228</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3609,7 +3597,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3629,7 +3617,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>139</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3666,10 +3654,10 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,7 +3674,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>98</v>
@@ -3709,7 +3697,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3729,7 +3717,7 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3749,7 +3737,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,10 +3754,10 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3786,10 +3774,10 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,7 +3797,7 @@
         <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3829,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3849,7 +3837,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,7 +3854,7 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>20</v>
@@ -3886,10 +3874,10 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3909,7 +3897,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3929,7 +3917,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3949,7 +3937,7 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3966,7 +3954,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>20</v>
@@ -3986,10 +3974,10 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4009,7 +3997,7 @@
         <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4029,7 +4017,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4049,7 +4037,7 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4066,10 +4054,10 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4086,10 +4074,10 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4109,7 +4097,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,7 +4117,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4149,7 +4137,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4166,7 +4154,7 @@
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>20</v>
@@ -4186,10 +4174,10 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4229,7 +4217,7 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,10 +4254,10 @@
         <v>23</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>136</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,10 +4274,10 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4309,7 +4297,7 @@
         <v>33</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4329,7 +4317,7 @@
         <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>228</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4349,7 +4337,7 @@
         <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4366,10 +4354,10 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4386,10 +4374,10 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,7 +4397,7 @@
         <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4429,7 +4417,7 @@
         <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4449,7 +4437,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4466,10 +4454,10 @@
         <v>23</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4486,7 +4474,7 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4509,7 +4497,7 @@
         <v>39</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4526,10 +4514,10 @@
         <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4546,10 +4534,10 @@
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4569,7 +4557,7 @@
         <v>42</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,10 +4574,10 @@
         <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4606,10 +4594,10 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4646,10 +4634,10 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4666,7 +4654,7 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4689,7 +4677,7 @@
         <v>49</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4706,10 +4694,10 @@
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4726,7 +4714,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>12</v>
@@ -4746,10 +4734,10 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,18 +4754,18 @@
         <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>12</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4786,7 +4774,7 @@
         <v>23</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>12</v>
@@ -4794,22 +4782,22 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>353</v>
+        <v>43</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4823,13 +4811,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4846,10 +4834,10 @@
         <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4866,10 +4854,10 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4886,10 +4874,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4906,10 +4894,10 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4926,7 +4914,7 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>43</v>
@@ -4946,7 +4934,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>43</v>
@@ -4966,7 +4954,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>43</v>
@@ -4986,10 +4974,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5006,10 +4994,10 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5026,10 +5014,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5046,10 +5034,10 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5066,10 +5054,10 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>43</v>
+        <v>226</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5083,13 +5071,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5103,13 +5091,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5126,7 +5114,7 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>12</v>
@@ -5146,10 +5134,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5166,7 +5154,7 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>12</v>
@@ -5186,10 +5174,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5206,10 +5194,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5226,10 +5214,10 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5246,7 +5234,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
@@ -5266,10 +5254,10 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5286,49 +5274,9 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F185" s="1" t="s">
         <v>107</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="401">
   <si>
     <t/>
   </si>
@@ -61,7 +61,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-8B)</t>
+    <t>PT,(E-3B)</t>
   </si>
   <si>
     <t>10002047</t>
@@ -689,9 +689,6 @@
   </si>
   <si>
     <t>SALONPAS KOYO 5X2'S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
   </si>
   <si>
     <t>20063736</t>
@@ -3537,15 +3534,15 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3557,15 +3554,15 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3582,10 +3579,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3602,10 +3599,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3617,15 +3614,15 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3642,10 +3639,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3662,10 +3659,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3682,10 +3679,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3697,15 +3694,15 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3722,10 +3719,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3737,15 +3734,15 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3762,10 +3759,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3782,10 +3779,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3802,10 +3799,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3822,10 +3819,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3842,10 +3839,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3862,10 +3859,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3882,10 +3879,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3902,10 +3899,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3922,10 +3919,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3942,10 +3939,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3962,10 +3959,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3982,10 +3979,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4002,10 +3999,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4022,10 +4019,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4042,10 +4039,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4062,10 +4059,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4082,10 +4079,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4102,10 +4099,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4122,10 +4119,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4142,10 +4139,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4162,10 +4159,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4182,10 +4179,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4202,10 +4199,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4222,10 +4219,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4242,10 +4239,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4257,15 +4254,15 @@
         <v>33</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4277,15 +4274,15 @@
         <v>33</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4302,10 +4299,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4322,10 +4319,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4342,10 +4339,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4362,10 +4359,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4382,10 +4379,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4402,10 +4399,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4422,10 +4419,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4442,10 +4439,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4462,10 +4459,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4482,10 +4479,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4502,10 +4499,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4522,10 +4519,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4542,10 +4539,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4562,10 +4559,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4582,10 +4579,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4602,10 +4599,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4622,10 +4619,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4642,10 +4639,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4662,10 +4659,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4682,10 +4679,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4702,10 +4699,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4722,10 +4719,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4742,10 +4739,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4757,15 +4754,15 @@
         <v>56</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4782,10 +4779,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4802,10 +4799,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -4822,10 +4819,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -4842,10 +4839,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -4862,10 +4859,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -4882,10 +4879,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -4902,10 +4899,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -4922,10 +4919,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -4942,10 +4939,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -4962,10 +4959,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -4982,10 +4979,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5002,10 +4999,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5022,10 +5019,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5042,10 +5039,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5057,15 +5054,15 @@
         <v>49</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5082,10 +5079,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5102,10 +5099,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5122,10 +5119,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5142,10 +5139,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5162,10 +5159,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5182,10 +5179,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5202,10 +5199,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5222,10 +5219,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5242,10 +5239,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5262,10 +5259,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="395">
   <si>
     <t/>
   </si>
@@ -415,30 +415,24 @@
     <t>INSTO COOL 7.5ML</t>
   </si>
   <si>
-    <t>20129405</t>
-  </si>
-  <si>
-    <t>VICKS JAHE MADU 105</t>
+    <t>20120782</t>
+  </si>
+  <si>
+    <t>VICKS JAHE MADU 56ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000144</t>
+  </si>
+  <si>
+    <t>VICKS F44 DWSA 54ML</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>20120782</t>
-  </si>
-  <si>
-    <t>VICKS JAHE MADU 56ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000144</t>
-  </si>
-  <si>
-    <t>VICKS F44 DWSA 54ML</t>
-  </si>
-  <si>
     <t>20128049</t>
   </si>
   <si>
@@ -889,12 +883,6 @@
     <t>IM-BOOST VIT C&amp;D3 4S</t>
   </si>
   <si>
-    <t>20137414</t>
-  </si>
-  <si>
-    <t>DOLO NEUROBION 10S</t>
-  </si>
-  <si>
     <t>20141957</t>
   </si>
   <si>
@@ -907,12 +895,6 @@
     <t>KONIDIN OBAT BTK 4'S</t>
   </si>
   <si>
-    <t>10010246</t>
-  </si>
-  <si>
-    <t>NEUROBION VIT.10'S</t>
-  </si>
-  <si>
     <t>20027551</t>
   </si>
   <si>
@@ -1093,13 +1075,13 @@
     <t>10002941</t>
   </si>
   <si>
-    <t>C/LANG KAYU PUTIH120</t>
+    <t>C/LANG MIKAPU 120 ML</t>
   </si>
   <si>
     <t>10000425</t>
   </si>
   <si>
-    <t>C/LANG KAYU PUTIH 60</t>
+    <t>C/LANG MIKAPU 60 ML</t>
   </si>
   <si>
     <t>20079757</t>
@@ -1606,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2691,7 +2673,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>136</v>
@@ -2711,7 +2693,7 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>139</v>
@@ -2731,10 +2713,10 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2751,10 +2733,10 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2771,10 +2753,10 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2791,10 +2773,10 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2811,10 +2793,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2831,10 +2813,10 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2851,10 +2833,10 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2871,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2891,10 +2873,10 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2911,10 +2893,10 @@
         <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2931,10 +2913,10 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2951,10 +2933,10 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2971,10 +2953,10 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2991,10 +2973,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3008,13 +2990,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3031,7 +3013,7 @@
         <v>19</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3051,7 +3033,7 @@
         <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3071,7 +3053,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3091,7 +3073,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3111,7 +3093,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3131,7 +3113,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3151,7 +3133,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3171,7 +3153,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3191,7 +3173,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3211,7 +3193,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3231,7 +3213,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3251,10 +3233,10 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3271,7 +3253,7 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>98</v>
@@ -3291,7 +3273,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>98</v>
@@ -3311,10 +3293,10 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3331,7 +3313,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
@@ -3351,7 +3333,7 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
@@ -3371,10 +3353,10 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3391,18 +3373,18 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3411,18 +3393,18 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3431,18 +3413,18 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3451,30 +3433,30 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,7 +3476,7 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3514,7 +3496,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3551,10 +3533,10 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,7 +3556,7 @@
         <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,7 +3576,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,7 +3596,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3631,10 +3613,10 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,7 +3636,7 @@
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,7 +3656,7 @@
         <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,7 +3676,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3714,7 +3696,7 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3731,10 +3713,10 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3754,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3774,7 +3756,7 @@
         <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3794,7 +3776,7 @@
         <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3831,7 +3813,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>20</v>
@@ -3854,7 +3836,7 @@
         <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,7 +3856,7 @@
         <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,7 +3876,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,7 +3913,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>20</v>
@@ -3954,7 +3936,7 @@
         <v>23</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,7 +3956,7 @@
         <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,7 +3976,7 @@
         <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,7 +3996,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,10 +4013,10 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4054,7 +4036,7 @@
         <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4074,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,7 +4076,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,7 +4113,7 @@
         <v>23</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>20</v>
@@ -4154,7 +4136,7 @@
         <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,7 +4156,7 @@
         <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4211,10 +4193,10 @@
         <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,10 +4213,10 @@
         <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,7 +4236,7 @@
         <v>33</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4274,7 +4256,7 @@
         <v>33</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4291,10 +4273,10 @@
         <v>23</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,10 +4293,10 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,10 +4313,10 @@
         <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4374,7 +4356,7 @@
         <v>36</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4391,10 +4373,10 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,10 +4393,10 @@
         <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,10 +4413,10 @@
         <v>23</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4451,7 +4433,7 @@
         <v>23</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>12</v>
@@ -4471,10 +4453,10 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4491,7 +4473,7 @@
         <v>23</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>20</v>
@@ -4511,10 +4493,10 @@
         <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4531,10 +4513,10 @@
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4551,10 +4533,10 @@
         <v>23</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4571,10 +4553,10 @@
         <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,10 +4573,10 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,10 +4593,10 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4631,10 +4613,10 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4651,10 +4633,10 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,7 +4653,7 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>12</v>
@@ -4691,18 +4673,18 @@
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>20</v>
+        <v>342</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4711,7 +4693,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>12</v>
@@ -4719,42 +4701,42 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>348</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4768,13 +4750,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4791,10 +4773,10 @@
         <v>26</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4811,7 +4793,7 @@
         <v>26</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>43</v>
@@ -4831,10 +4813,10 @@
         <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4851,10 +4833,10 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4871,7 +4853,7 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>43</v>
@@ -4891,7 +4873,7 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>43</v>
@@ -4911,10 +4893,10 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4931,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4951,7 +4933,7 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>43</v>
@@ -4971,10 +4953,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4991,10 +4973,10 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5008,13 +4990,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5028,13 +5010,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5048,13 +5030,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5071,10 +5053,10 @@
         <v>29</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5091,10 +5073,10 @@
         <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5111,7 +5093,7 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>12</v>
@@ -5131,10 +5113,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5151,10 +5133,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5171,10 +5153,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5191,10 +5173,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5211,69 +5193,9 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F183" s="1" t="s">
         <v>107</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -1075,13 +1075,13 @@
     <t>10002941</t>
   </si>
   <si>
-    <t>C/LANG MIKAPU 120 ML</t>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>10000425</t>
   </si>
   <si>
-    <t>C/LANG MIKAPU 60 ML</t>
+    <t>C/LANG KAYU PUTIH 60</t>
   </si>
   <si>
     <t>20079757</t>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="399">
   <si>
     <t/>
   </si>
@@ -301,6 +301,15 @@
     <t>EJ SPORT ORANGE 2S</t>
   </si>
   <si>
+    <t>20039339</t>
+  </si>
+  <si>
+    <t>SILADEX O/B EXP 60</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
     <t>10030787</t>
   </si>
   <si>
@@ -334,9 +343,6 @@
     <t>TERMOREX PLUS 60 ML</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
     <t>10006565</t>
   </si>
   <si>
@@ -415,6 +421,12 @@
     <t>INSTO COOL 7.5ML</t>
   </si>
   <si>
+    <t>20017270</t>
+  </si>
+  <si>
+    <t>VICKS F44 ANK STRW54</t>
+  </si>
+  <si>
     <t>20120782</t>
   </si>
   <si>
@@ -499,12 +511,6 @@
     <t>WOODS O/B LIQ NTRL60</t>
   </si>
   <si>
-    <t>20039339</t>
-  </si>
-  <si>
-    <t>SILADEX O/B EXP 60</t>
-  </si>
-  <si>
     <t>20124758</t>
   </si>
   <si>
@@ -667,22 +673,52 @@
     <t>23</t>
   </si>
   <si>
+    <t>10000077</t>
+  </si>
+  <si>
+    <t>BODREX SKT KEPALA 20</t>
+  </si>
+  <si>
     <t>10000473</t>
   </si>
   <si>
     <t>BODREXIN OBAT JRK12S</t>
   </si>
   <si>
+    <t>10034123</t>
+  </si>
+  <si>
+    <t>SALONPAS KOYO 5X2'S</t>
+  </si>
+  <si>
+    <t>20128440</t>
+  </si>
+  <si>
+    <t>SALONPAS EX.HOT 5X2S</t>
+  </si>
+  <si>
+    <t>10000098</t>
+  </si>
+  <si>
+    <t>CABE KOYO KECIL (10)</t>
+  </si>
+  <si>
     <t>10008683</t>
   </si>
   <si>
     <t>PANADOL CAPLET EXT10</t>
   </si>
   <si>
-    <t>10034123</t>
-  </si>
-  <si>
-    <t>SALONPAS KOYO 5X2'S</t>
+    <t>20027661</t>
+  </si>
+  <si>
+    <t>BODREX EXTRA 4'S</t>
+  </si>
+  <si>
+    <t>20052425</t>
+  </si>
+  <si>
+    <t>SALONPAS KOYO 10X2'S</t>
   </si>
   <si>
     <t>20063736</t>
@@ -691,10 +727,10 @@
     <t>SALONPAS PAIN REL 5S</t>
   </si>
   <si>
-    <t>10000077</t>
-  </si>
-  <si>
-    <t>BODREX SKT KEPALA 20</t>
+    <t>10000073</t>
+  </si>
+  <si>
+    <t>PARAMEX SKT KEPALA 4</t>
   </si>
   <si>
     <t>10040122</t>
@@ -703,22 +739,34 @@
     <t>HISAMITSU KMPRS BABY</t>
   </si>
   <si>
-    <t>20052425</t>
-  </si>
-  <si>
-    <t>SALONPAS KOYO 10X2'S</t>
-  </si>
-  <si>
     <t>20069792</t>
   </si>
   <si>
     <t>PANADOL FLU&amp;BTK 10'S</t>
   </si>
   <si>
-    <t>10000098</t>
-  </si>
-  <si>
-    <t>CABE KOYO KECIL (10)</t>
+    <t>20141639</t>
+  </si>
+  <si>
+    <t>SKTONIK ACTV GUMMY6S</t>
+  </si>
+  <si>
+    <t>20142949</t>
+  </si>
+  <si>
+    <t>CNTRPAIN MD.PLST 10S</t>
+  </si>
+  <si>
+    <t>10000155</t>
+  </si>
+  <si>
+    <t>DECOLGEN TABLET(4'S)</t>
+  </si>
+  <si>
+    <t>10000621</t>
+  </si>
+  <si>
+    <t>SANGOBION (10'S)</t>
   </si>
   <si>
     <t>10004359</t>
@@ -733,30 +781,30 @@
     <t>HISAMITSU KMP/DM PCS</t>
   </si>
   <si>
-    <t>20027661</t>
-  </si>
-  <si>
-    <t>BODREX EXTRA 4'S</t>
-  </si>
-  <si>
-    <t>20128440</t>
-  </si>
-  <si>
-    <t>SALONPAS EX.HOT 5X2S</t>
-  </si>
-  <si>
-    <t>10000073</t>
-  </si>
-  <si>
-    <t>PARAMEX SKT KEPALA 4</t>
-  </si>
-  <si>
     <t>20065430</t>
   </si>
   <si>
     <t>HNSAPLAST AQUA PRO 6</t>
   </si>
   <si>
+    <t>10000154</t>
+  </si>
+  <si>
+    <t>NEOZEP FORTE STR.4'S</t>
+  </si>
+  <si>
+    <t>10003514</t>
+  </si>
+  <si>
+    <t>H/PLAST KAIN ELAST10</t>
+  </si>
+  <si>
+    <t>20112905</t>
+  </si>
+  <si>
+    <t>FATIGON SPIRIT 6'S</t>
+  </si>
+  <si>
     <t>20129404</t>
   </si>
   <si>
@@ -769,16 +817,10 @@
     <t>ANTIMO ANAK JERUK5'S</t>
   </si>
   <si>
-    <t>20141639</t>
-  </si>
-  <si>
-    <t>SKTONIK ACTV GUMMY6S</t>
-  </si>
-  <si>
-    <t>10000155</t>
-  </si>
-  <si>
-    <t>DECOLGEN TABLET(4'S)</t>
+    <t>10000452</t>
+  </si>
+  <si>
+    <t>ULTRA FLU 4'S</t>
   </si>
   <si>
     <t>10000555</t>
@@ -787,16 +829,10 @@
     <t>ANTIMO 10'S</t>
   </si>
   <si>
-    <t>10000621</t>
-  </si>
-  <si>
-    <t>SANGOBION (10'S)</t>
-  </si>
-  <si>
-    <t>10003514</t>
-  </si>
-  <si>
-    <t>H/PLAST KAIN ELAST10</t>
+    <t>10035326</t>
+  </si>
+  <si>
+    <t>HEMAVITON STAMINA5'S</t>
   </si>
   <si>
     <t>20044054</t>
@@ -805,10 +841,16 @@
     <t>C/LANG KOOLFEVER BYI</t>
   </si>
   <si>
-    <t>10000154</t>
-  </si>
-  <si>
-    <t>NEOZEP FORTE STR.4'S</t>
+    <t>20133187</t>
+  </si>
+  <si>
+    <t>H/PLAST KAIN FUN10'S</t>
+  </si>
+  <si>
+    <t>10003995</t>
+  </si>
+  <si>
+    <t>HEMAVITON ACTION 5'S</t>
   </si>
   <si>
     <t>10028800</t>
@@ -823,28 +865,28 @@
     <t>C/LANG KOOLFEVER ANK</t>
   </si>
   <si>
-    <t>20112905</t>
-  </si>
-  <si>
-    <t>FATIGON SPIRIT 6'S</t>
-  </si>
-  <si>
-    <t>20133187</t>
-  </si>
-  <si>
-    <t>H/PLAST KAIN FUN10'S</t>
-  </si>
-  <si>
-    <t>10000452</t>
-  </si>
-  <si>
-    <t>ULTRA FLU 4'S</t>
-  </si>
-  <si>
-    <t>10035326</t>
-  </si>
-  <si>
-    <t>HEMAVITON STAMINA5'S</t>
+    <t>20137316</t>
+  </si>
+  <si>
+    <t>HNSPLST  TRANSP 10'S</t>
+  </si>
+  <si>
+    <t>20141957</t>
+  </si>
+  <si>
+    <t>ULTRA FLU STR 10S</t>
+  </si>
+  <si>
+    <t>10000075</t>
+  </si>
+  <si>
+    <t>KONIDIN OBAT BTK 4'S</t>
+  </si>
+  <si>
+    <t>20053803</t>
+  </si>
+  <si>
+    <t>NEUROBION FORTE 10'S</t>
   </si>
   <si>
     <t>20113365</t>
@@ -853,46 +895,28 @@
     <t>PROMAG 10'S</t>
   </si>
   <si>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
+  </si>
+  <si>
     <t>20122436</t>
   </si>
   <si>
     <t>CL KOOL FEVER DEWASA</t>
   </si>
   <si>
-    <t>20137316</t>
-  </si>
-  <si>
-    <t>HNSPLST  TRANSP 10'S</t>
-  </si>
-  <si>
     <t>10000665</t>
   </si>
   <si>
     <t>MYLANTA OBAT MAAG 10</t>
   </si>
   <si>
-    <t>10003995</t>
-  </si>
-  <si>
-    <t>HEMAVITON ACTION 5'S</t>
-  </si>
-  <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
-  </si>
-  <si>
-    <t>20141957</t>
-  </si>
-  <si>
-    <t>ULTRA FLU STR 10S</t>
-  </si>
-  <si>
-    <t>10000075</t>
-  </si>
-  <si>
-    <t>KONIDIN OBAT BTK 4'S</t>
+    <t>10030867</t>
+  </si>
+  <si>
+    <t>PROCOLD OBAT FLU 6'S</t>
   </si>
   <si>
     <t>20027551</t>
@@ -907,34 +931,52 @@
     <t>IM-BOOST TABLET 4'S</t>
   </si>
   <si>
+    <t>20102471</t>
+  </si>
+  <si>
+    <t>CDR VITAMIN C 2'S</t>
+  </si>
+  <si>
+    <t>10003650</t>
+  </si>
+  <si>
+    <t>ENERVON C TABLET 4'S</t>
+  </si>
+  <si>
+    <t>20010358</t>
+  </si>
+  <si>
+    <t>MXAGRIP FLU&amp;BATUK 4S</t>
+  </si>
+  <si>
+    <t>20056311</t>
+  </si>
+  <si>
+    <t>CEREBRF.GUMMY STR20G</t>
+  </si>
+  <si>
     <t>20120361</t>
   </si>
   <si>
     <t>ENTROSTOP STR 10'S</t>
   </si>
   <si>
-    <t>10003650</t>
-  </si>
-  <si>
-    <t>ENERVON C TABLET 4'S</t>
-  </si>
-  <si>
-    <t>10030867</t>
-  </si>
-  <si>
-    <t>PROCOLD OBAT FLU 6'S</t>
-  </si>
-  <si>
-    <t>20053803</t>
-  </si>
-  <si>
-    <t>NEUROBION FORTE 10'S</t>
-  </si>
-  <si>
-    <t>20056311</t>
-  </si>
-  <si>
-    <t>CEREBRF.GUMMY STR20G</t>
+    <t>20124298</t>
+  </si>
+  <si>
+    <t>IM-BOOST BONE ORG 2S</t>
+  </si>
+  <si>
+    <t>10000069</t>
+  </si>
+  <si>
+    <t>MIXAGRIP O.SKT FLU4S</t>
+  </si>
+  <si>
+    <t>20083486</t>
+  </si>
+  <si>
+    <t>REDOXON JERUK 2'S</t>
   </si>
   <si>
     <t>20090384</t>
@@ -943,10 +985,10 @@
     <t>DIAPET KAPSUL 10'S</t>
   </si>
   <si>
-    <t>20010358</t>
-  </si>
-  <si>
-    <t>MXAGRIP FLU&amp;BATUK 4S</t>
+    <t>20057705</t>
+  </si>
+  <si>
+    <t>KONIDIN OBAT BTK 5X7</t>
   </si>
   <si>
     <t>20090383</t>
@@ -955,16 +997,10 @@
     <t>LAXING STR 10'S</t>
   </si>
   <si>
-    <t>20102471</t>
-  </si>
-  <si>
-    <t>CDR VITAMIN C 2'S</t>
-  </si>
-  <si>
-    <t>10000069</t>
-  </si>
-  <si>
-    <t>MIXAGRIP O.SKT FLU4S</t>
+    <t>20111900</t>
+  </si>
+  <si>
+    <t>IM-BOOST EFF ORG 2'S</t>
   </si>
   <si>
     <t>20014241</t>
@@ -973,10 +1009,16 @@
     <t>AMBEVEN U/ WASR 10'S</t>
   </si>
   <si>
-    <t>20124298</t>
-  </si>
-  <si>
-    <t>IM-BOOST BONE ORG 2S</t>
+    <t>20132440</t>
+  </si>
+  <si>
+    <t>ULTRA CAP GOLD VIT4S</t>
+  </si>
+  <si>
+    <t>20140912</t>
+  </si>
+  <si>
+    <t>SM TOLAK ANGIN 15ML</t>
   </si>
   <si>
     <t>20048747</t>
@@ -985,34 +1027,16 @@
     <t>MICROLAX GEL 5ML</t>
   </si>
   <si>
-    <t>20057705</t>
-  </si>
-  <si>
-    <t>KONIDIN OBAT BTK 5X7</t>
-  </si>
-  <si>
-    <t>20083486</t>
-  </si>
-  <si>
-    <t>REDOXON JERUK 2'S</t>
-  </si>
-  <si>
     <t>10000197</t>
   </si>
   <si>
     <t>VITACIMIN STRIP 2'S</t>
   </si>
   <si>
-    <t>20132440</t>
-  </si>
-  <si>
-    <t>ULTRA CAP GOLD VIT4S</t>
-  </si>
-  <si>
-    <t>20140912</t>
-  </si>
-  <si>
-    <t>SM TOLAK ANGIN 15ML</t>
+    <t>20124837</t>
+  </si>
+  <si>
+    <t>KALPANAX SALEP 6G</t>
   </si>
   <si>
     <t>10003980</t>
@@ -1021,31 +1045,19 @@
     <t>VICEE VIT C LEMON 2S</t>
   </si>
   <si>
-    <t>20124837</t>
-  </si>
-  <si>
-    <t>KALPANAX SALEP 6G</t>
+    <t>10037415</t>
+  </si>
+  <si>
+    <t>88 SALEP KULIT 6G</t>
+  </si>
+  <si>
+    <t>RT,(E-13B)</t>
   </si>
   <si>
     <t>10002862</t>
   </si>
   <si>
     <t>XON-CE VIT.C500MG2'S</t>
-  </si>
-  <si>
-    <t>10037415</t>
-  </si>
-  <si>
-    <t>88 SALEP KULIT 6G</t>
-  </si>
-  <si>
-    <t>RT,(E-13B)</t>
-  </si>
-  <si>
-    <t>20111900</t>
-  </si>
-  <si>
-    <t>IM-BOOST EFF ORG 2'S</t>
   </si>
   <si>
     <t>20082403</t>
@@ -1588,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2336,15 +2348,15 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2361,10 +2373,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2381,10 +2393,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2396,7 +2408,7 @@
         <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2416,7 +2428,7 @@
         <v>23</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2436,7 +2448,7 @@
         <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2456,7 +2468,7 @@
         <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2496,7 +2508,7 @@
         <v>36</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2516,7 +2528,7 @@
         <v>39</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2536,7 +2548,7 @@
         <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2556,7 +2568,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2670,21 +2682,21 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2693,18 +2705,18 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2713,18 +2725,18 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2733,10 +2745,10 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2753,10 +2765,10 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2773,10 +2785,10 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2793,10 +2805,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2813,10 +2825,10 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2833,10 +2845,10 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,10 +2865,10 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,10 +2885,10 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2893,10 +2905,10 @@
         <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,10 +2925,10 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,10 +2945,10 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,10 +2965,10 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,10 +2985,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2990,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3013,7 +3025,7 @@
         <v>19</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3033,7 +3045,7 @@
         <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3053,7 +3065,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3073,7 +3085,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3093,7 +3105,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3113,7 +3125,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3133,7 +3145,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3153,7 +3165,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3173,7 +3185,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3193,7 +3205,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3213,7 +3225,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3233,10 +3245,10 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3253,10 +3265,10 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3273,10 +3285,10 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3293,10 +3305,10 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3313,7 +3325,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
@@ -3333,7 +3345,7 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
@@ -3353,10 +3365,10 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3373,18 +3385,18 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>208</v>
+        <v>65</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3393,18 +3405,18 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3413,18 +3425,18 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3433,30 +3445,30 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3476,7 +3488,7 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3496,7 +3508,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3533,10 +3545,10 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3556,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,7 +3588,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,7 +3608,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3613,10 +3625,10 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3633,10 +3645,10 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,7 +3668,7 @@
         <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,7 +3688,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,7 +3708,7 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3713,10 +3725,10 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3733,10 +3745,10 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,7 +3768,7 @@
         <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3776,7 +3788,7 @@
         <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,10 +3825,10 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,10 +3845,10 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,7 +3868,7 @@
         <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3896,7 +3908,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3913,10 +3925,10 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,10 +3945,10 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3956,7 +3968,7 @@
         <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,7 +4008,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4025,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>20</v>
@@ -4033,10 +4045,10 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4056,7 +4068,7 @@
         <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4076,7 +4088,7 @@
         <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4096,7 +4108,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,7 +4125,7 @@
         <v>23</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>20</v>
@@ -4133,10 +4145,10 @@
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,7 +4168,7 @@
         <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4176,7 +4188,7 @@
         <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,10 +4205,10 @@
         <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,10 +4225,10 @@
         <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4233,10 +4245,10 @@
         <v>23</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,10 +4285,10 @@
         <v>23</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,10 +4305,10 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,10 +4325,10 @@
         <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4345,7 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>20</v>
@@ -4356,7 +4368,7 @@
         <v>36</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,7 +4385,7 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>12</v>
@@ -4393,10 +4405,10 @@
         <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4413,7 +4425,7 @@
         <v>23</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>20</v>
@@ -4433,10 +4445,10 @@
         <v>23</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,10 +4465,10 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,10 +4485,10 @@
         <v>23</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,7 +4505,7 @@
         <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4513,10 +4525,10 @@
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4533,7 +4545,7 @@
         <v>23</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4553,10 +4565,10 @@
         <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4573,10 +4585,10 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,10 +4605,10 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4613,10 +4625,10 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,10 +4645,10 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,10 +4665,10 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4673,19 +4685,19 @@
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>342</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
@@ -4693,30 +4705,30 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4730,13 +4742,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,10 +4765,10 @@
         <v>26</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,10 +4785,10 @@
         <v>26</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4793,10 +4805,10 @@
         <v>26</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,10 +4825,10 @@
         <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,7 +4845,7 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>43</v>
@@ -4853,7 +4865,7 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>43</v>
@@ -4873,7 +4885,7 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>43</v>
@@ -4893,10 +4905,10 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,10 +4925,10 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4933,10 +4945,10 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,10 +4965,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,10 +4985,10 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4990,13 +5002,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5010,13 +5022,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5033,7 +5045,7 @@
         <v>29</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>12</v>
@@ -5053,10 +5065,10 @@
         <v>29</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,7 +5085,7 @@
         <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>12</v>
@@ -5093,10 +5105,10 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,10 +5125,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5133,10 +5145,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5153,7 +5165,7 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>20</v>
@@ -5173,10 +5185,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5193,10 +5205,50 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>107</v>
+      <c r="F182" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
   <si>
     <t/>
   </si>
@@ -475,6 +475,12 @@
     <t>VICKS VAPORUB 50G</t>
   </si>
   <si>
+    <t>20143018</t>
+  </si>
+  <si>
+    <t>VCKS VPRB EXSTRG 25G</t>
+  </si>
+  <si>
     <t>10000289</t>
   </si>
   <si>
@@ -679,6 +685,12 @@
     <t>BODREX SKT KEPALA 20</t>
   </si>
   <si>
+    <t>10000098</t>
+  </si>
+  <si>
+    <t>CABE KOYO KECIL (10)</t>
+  </si>
+  <si>
     <t>10000473</t>
   </si>
   <si>
@@ -697,12 +709,6 @@
     <t>SALONPAS EX.HOT 5X2S</t>
   </si>
   <si>
-    <t>10000098</t>
-  </si>
-  <si>
-    <t>CABE KOYO KECIL (10)</t>
-  </si>
-  <si>
     <t>10008683</t>
   </si>
   <si>
@@ -727,12 +733,24 @@
     <t>SALONPAS PAIN REL 5S</t>
   </si>
   <si>
+    <t>20141639</t>
+  </si>
+  <si>
+    <t>SKTONIK ACTV GUMMY6S</t>
+  </si>
+  <si>
     <t>10000073</t>
   </si>
   <si>
     <t>PARAMEX SKT KEPALA 4</t>
   </si>
   <si>
+    <t>10000621</t>
+  </si>
+  <si>
+    <t>SANGOBION (10'S)</t>
+  </si>
+  <si>
     <t>10040122</t>
   </si>
   <si>
@@ -745,12 +763,6 @@
     <t>PANADOL FLU&amp;BTK 10'S</t>
   </si>
   <si>
-    <t>20141639</t>
-  </si>
-  <si>
-    <t>SKTONIK ACTV GUMMY6S</t>
-  </si>
-  <si>
     <t>20142949</t>
   </si>
   <si>
@@ -763,12 +775,6 @@
     <t>DECOLGEN TABLET(4'S)</t>
   </si>
   <si>
-    <t>10000621</t>
-  </si>
-  <si>
-    <t>SANGOBION (10'S)</t>
-  </si>
-  <si>
     <t>10004359</t>
   </si>
   <si>
@@ -787,6 +793,12 @@
     <t>HNSAPLAST AQUA PRO 6</t>
   </si>
   <si>
+    <t>20112905</t>
+  </si>
+  <si>
+    <t>FATIGON SPIRIT 6'S</t>
+  </si>
+  <si>
     <t>10000154</t>
   </si>
   <si>
@@ -799,10 +811,10 @@
     <t>H/PLAST KAIN ELAST10</t>
   </si>
   <si>
-    <t>20112905</t>
-  </si>
-  <si>
-    <t>FATIGON SPIRIT 6'S</t>
+    <t>10035326</t>
+  </si>
+  <si>
+    <t>HEMAVITON STAMINA5'S</t>
   </si>
   <si>
     <t>20129404</t>
@@ -829,10 +841,10 @@
     <t>ANTIMO 10'S</t>
   </si>
   <si>
-    <t>10035326</t>
-  </si>
-  <si>
-    <t>HEMAVITON STAMINA5'S</t>
+    <t>10003995</t>
+  </si>
+  <si>
+    <t>HEMAVITON ACTION 5'S</t>
   </si>
   <si>
     <t>20044054</t>
@@ -847,12 +859,6 @@
     <t>H/PLAST KAIN FUN10'S</t>
   </si>
   <si>
-    <t>10003995</t>
-  </si>
-  <si>
-    <t>HEMAVITON ACTION 5'S</t>
-  </si>
-  <si>
     <t>10028800</t>
   </si>
   <si>
@@ -865,6 +871,12 @@
     <t>C/LANG KOOLFEVER ANK</t>
   </si>
   <si>
+    <t>20053803</t>
+  </si>
+  <si>
+    <t>NEUROBION FORTE 10'S</t>
+  </si>
+  <si>
     <t>20137316</t>
   </si>
   <si>
@@ -883,10 +895,10 @@
     <t>KONIDIN OBAT BTK 4'S</t>
   </si>
   <si>
-    <t>20053803</t>
-  </si>
-  <si>
-    <t>NEUROBION FORTE 10'S</t>
+    <t>20102471</t>
+  </si>
+  <si>
+    <t>CDR VITAMIN C 2'S</t>
   </si>
   <si>
     <t>20113365</t>
@@ -931,10 +943,10 @@
     <t>IM-BOOST TABLET 4'S</t>
   </si>
   <si>
-    <t>20102471</t>
-  </si>
-  <si>
-    <t>CDR VITAMIN C 2'S</t>
+    <t>20124298</t>
+  </si>
+  <si>
+    <t>IM-BOOST BONE ORG 2S</t>
   </si>
   <si>
     <t>10003650</t>
@@ -955,36 +967,36 @@
     <t>CEREBRF.GUMMY STR20G</t>
   </si>
   <si>
+    <t>20083486</t>
+  </si>
+  <si>
+    <t>REDOXON JERUK 2'S</t>
+  </si>
+  <si>
     <t>20120361</t>
   </si>
   <si>
     <t>ENTROSTOP STR 10'S</t>
   </si>
   <si>
-    <t>20124298</t>
-  </si>
-  <si>
-    <t>IM-BOOST BONE ORG 2S</t>
-  </si>
-  <si>
     <t>10000069</t>
   </si>
   <si>
     <t>MIXAGRIP O.SKT FLU4S</t>
   </si>
   <si>
-    <t>20083486</t>
-  </si>
-  <si>
-    <t>REDOXON JERUK 2'S</t>
-  </si>
-  <si>
     <t>20090384</t>
   </si>
   <si>
     <t>DIAPET KAPSUL 10'S</t>
   </si>
   <si>
+    <t>20111900</t>
+  </si>
+  <si>
+    <t>IM-BOOST EFF ORG 2'S</t>
+  </si>
+  <si>
     <t>20057705</t>
   </si>
   <si>
@@ -997,10 +1009,10 @@
     <t>LAXING STR 10'S</t>
   </si>
   <si>
-    <t>20111900</t>
-  </si>
-  <si>
-    <t>IM-BOOST EFF ORG 2'S</t>
+    <t>20132440</t>
+  </si>
+  <si>
+    <t>ULTRA CAP GOLD VIT4S</t>
   </si>
   <si>
     <t>20014241</t>
@@ -1009,12 +1021,6 @@
     <t>AMBEVEN U/ WASR 10'S</t>
   </si>
   <si>
-    <t>20132440</t>
-  </si>
-  <si>
-    <t>ULTRA CAP GOLD VIT4S</t>
-  </si>
-  <si>
     <t>20140912</t>
   </si>
   <si>
@@ -1025,6 +1031,12 @@
   </si>
   <si>
     <t>MICROLAX GEL 5ML</t>
+  </si>
+  <si>
+    <t>20055623</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG SIRUP15</t>
   </si>
   <si>
     <t>10000197</t>
@@ -1600,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2865,10 +2877,10 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2885,10 +2897,10 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,7 +2917,7 @@
         <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2925,10 +2937,10 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2945,10 +2957,10 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2965,10 +2977,10 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2985,10 +2997,10 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3005,10 +3017,10 @@
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3022,13 +3034,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3045,7 +3057,7 @@
         <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3065,7 +3077,7 @@
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3085,7 +3097,7 @@
         <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3105,7 +3117,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3125,7 +3137,7 @@
         <v>19</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3145,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3165,7 +3177,7 @@
         <v>19</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3185,7 +3197,7 @@
         <v>19</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3205,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3225,7 +3237,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3245,7 +3257,7 @@
         <v>19</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3265,10 +3277,10 @@
         <v>19</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,7 +3297,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>101</v>
@@ -3305,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>101</v>
@@ -3325,10 +3337,10 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3345,7 +3357,7 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
@@ -3365,7 +3377,7 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
@@ -3385,10 +3397,10 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3405,18 +3417,18 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3425,18 +3437,18 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3445,18 +3457,18 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3465,30 +3477,30 @@
         <v>19</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3508,7 +3520,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3528,7 +3540,7 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3548,7 +3560,7 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3565,10 +3577,10 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3585,10 +3597,10 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3608,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3628,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3665,10 +3677,10 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3685,10 +3697,10 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3708,7 +3720,7 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3728,7 +3740,7 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3748,7 +3760,7 @@
         <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3765,10 +3777,10 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3785,10 +3797,10 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3808,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3828,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3848,7 +3860,7 @@
         <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3865,10 +3877,10 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3885,10 +3897,10 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3908,7 +3920,7 @@
         <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3928,7 +3940,7 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3948,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,10 +3977,10 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,10 +3997,10 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4008,7 +4020,7 @@
         <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4028,7 +4040,7 @@
         <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4048,7 +4060,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,10 +4077,10 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,10 +4097,10 @@
         <v>23</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4108,7 +4120,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4128,7 +4140,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4148,7 +4160,7 @@
         <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4165,10 +4177,10 @@
         <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4185,10 +4197,10 @@
         <v>23</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4208,7 +4220,7 @@
         <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4248,7 +4260,7 @@
         <v>29</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4265,7 +4277,7 @@
         <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>20</v>
@@ -4285,10 +4297,10 @@
         <v>23</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4308,7 +4320,7 @@
         <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4328,7 +4340,7 @@
         <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4348,7 +4360,7 @@
         <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4365,10 +4377,10 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4385,10 +4397,10 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4428,7 +4440,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4465,10 +4477,10 @@
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4485,10 +4497,10 @@
         <v>23</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4508,7 +4520,7 @@
         <v>39</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4525,10 +4537,10 @@
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4545,10 +4557,10 @@
         <v>23</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4568,7 +4580,7 @@
         <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4585,10 +4597,10 @@
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,7 +4617,7 @@
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4628,7 +4640,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,10 +4657,10 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4665,10 +4677,10 @@
         <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4685,10 +4697,10 @@
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4705,10 +4717,10 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4725,19 +4737,19 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>346</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
@@ -4745,30 +4757,30 @@
         <v>23</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4782,13 +4794,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4805,10 +4817,10 @@
         <v>26</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4825,10 +4837,10 @@
         <v>26</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4845,10 +4857,10 @@
         <v>26</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4865,10 +4877,10 @@
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4885,7 +4897,7 @@
         <v>26</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>43</v>
@@ -4905,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>43</v>
@@ -4925,7 +4937,7 @@
         <v>26</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>43</v>
@@ -4945,10 +4957,10 @@
         <v>26</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4965,10 +4977,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4985,10 +4997,10 @@
         <v>26</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5005,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5025,10 +5037,10 @@
         <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5042,13 +5054,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,13 +5074,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5085,7 +5097,7 @@
         <v>29</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>12</v>
@@ -5105,10 +5117,10 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5125,7 +5137,7 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>12</v>
@@ -5145,10 +5157,10 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5165,10 +5177,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5185,10 +5197,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5205,7 +5217,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>20</v>
@@ -5225,10 +5237,10 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5245,9 +5257,49 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="F184" s="1" t="s">
         <v>98</v>
       </c>
     </row>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -310,79 +310,79 @@
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>10030787</t>
-  </si>
-  <si>
-    <t>ACTF PILEK&amp;BT.DHK 60</t>
+    <t>20143398</t>
+  </si>
+  <si>
+    <t>ACTF SYRUP PILEK 25</t>
+  </si>
+  <si>
+    <t>20138372</t>
+  </si>
+  <si>
+    <t>KOMIX OBH 6X7ML</t>
+  </si>
+  <si>
+    <t>20092712</t>
+  </si>
+  <si>
+    <t>KOMIX HERBAL 4X15ML</t>
+  </si>
+  <si>
+    <t>10008599</t>
+  </si>
+  <si>
+    <t>OBH/C ANAK STRW 60ML</t>
+  </si>
+  <si>
+    <t>10023206</t>
+  </si>
+  <si>
+    <t>TERMOREX PLUS 60 ML</t>
+  </si>
+  <si>
+    <t>10006565</t>
+  </si>
+  <si>
+    <t>TEMPRA T/PNS ANGR 60</t>
+  </si>
+  <si>
+    <t>10000548</t>
+  </si>
+  <si>
+    <t>CAP LANG NORIT (40)</t>
+  </si>
+  <si>
+    <t>10038823</t>
+  </si>
+  <si>
+    <t>COMBANTRIN JRK 10ML</t>
+  </si>
+  <si>
+    <t>20021454</t>
+  </si>
+  <si>
+    <t>MYLANTA MAAG MINT 50</t>
+  </si>
+  <si>
+    <t>20052643</t>
+  </si>
+  <si>
+    <t>PROMAG HRBAL BOX 6'S</t>
+  </si>
+  <si>
+    <t>20057840</t>
+  </si>
+  <si>
+    <t>POLYSILANE BTL 100</t>
+  </si>
+  <si>
+    <t>20021214</t>
+  </si>
+  <si>
+    <t>VGTA HERBAL ANGR 6'S</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138372</t>
-  </si>
-  <si>
-    <t>KOMIX OBH 6X7ML</t>
-  </si>
-  <si>
-    <t>20092712</t>
-  </si>
-  <si>
-    <t>KOMIX HERBAL 4X15ML</t>
-  </si>
-  <si>
-    <t>10008599</t>
-  </si>
-  <si>
-    <t>OBH/C ANAK STRW 60ML</t>
-  </si>
-  <si>
-    <t>10023206</t>
-  </si>
-  <si>
-    <t>TERMOREX PLUS 60 ML</t>
-  </si>
-  <si>
-    <t>10006565</t>
-  </si>
-  <si>
-    <t>TEMPRA T/PNS ANGR 60</t>
-  </si>
-  <si>
-    <t>10000548</t>
-  </si>
-  <si>
-    <t>CAP LANG NORIT (40)</t>
-  </si>
-  <si>
-    <t>10038823</t>
-  </si>
-  <si>
-    <t>COMBANTRIN JRK 10ML</t>
-  </si>
-  <si>
-    <t>20021454</t>
-  </si>
-  <si>
-    <t>MYLANTA MAAG MINT 50</t>
-  </si>
-  <si>
-    <t>20052643</t>
-  </si>
-  <si>
-    <t>PROMAG HRBAL BOX 6'S</t>
-  </si>
-  <si>
-    <t>20057840</t>
-  </si>
-  <si>
-    <t>POLYSILANE BTL 100</t>
-  </si>
-  <si>
-    <t>20021214</t>
-  </si>
-  <si>
-    <t>VGTA HERBAL ANGR 6'S</t>
   </si>
   <si>
     <t>20107145</t>
@@ -2360,15 +2360,15 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
         <v>46</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,7 +3300,7 @@
         <v>46</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,7 +3320,7 @@
         <v>49</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,7 +3340,7 @@
         <v>53</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>221</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3780,7 +3780,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3840,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,7 +3880,7 @@
         <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4720,7 +4720,7 @@
         <v>53</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -76,13 +76,22 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20139960</t>
+  </si>
+  <si>
+    <t>EJ SPORT ORANGE 2S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>10037376</t>
   </si>
   <si>
     <t>NATUR-E VIT ALMH 16</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>20073420</t>
@@ -91,7 +100,7 @@
     <t>NATUR-E 300 DN 16'S</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>20061582</t>
@@ -100,7 +109,7 @@
     <t>MADU TJ JYBEE JRK100</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>RT,(E-5B)</t>
@@ -112,7 +121,7 @@
     <t>CURCUMA GROW ORGE100</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>20137504</t>
@@ -121,7 +130,7 @@
     <t>SKTNK/ABC C.MADU 24S</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>10006069</t>
@@ -130,7 +139,7 @@
     <t>SAKATONIK STR 30X800</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>10016755</t>
@@ -139,7 +148,7 @@
     <t>GELIGA BALSAM OTOT20</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>RT,(E-6B)</t>
@@ -151,7 +160,7 @@
     <t>KALPANAX K CREAM 5GR</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>20094802</t>
@@ -160,7 +169,7 @@
     <t>88 KRIM ANTI JAMUR 5</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>RT,(E-7B)</t>
@@ -172,7 +181,7 @@
     <t>COUNTERPAIN CREAM 30</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>20047965</t>
@@ -181,7 +190,7 @@
     <t>HOT IN CREAM 120ML</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>20057841</t>
@@ -190,7 +199,7 @@
     <t>HOT IN CREAM 60G</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>20080244</t>
@@ -199,7 +208,448 @@
     <t>HOT IN CRM STRNG 120</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20054951</t>
+  </si>
+  <si>
+    <t>S/M TOLAK/A ANAK 5'S</t>
+  </si>
+  <si>
+    <t>20034577</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN+MDU 5'S</t>
+  </si>
+  <si>
+    <t>20122907</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN FLU 5'S</t>
+  </si>
+  <si>
+    <t>20064502</t>
+  </si>
+  <si>
+    <t>S/M TLK ANGIN BG 5'S</t>
+  </si>
+  <si>
+    <t>20064503</t>
+  </si>
+  <si>
+    <t>S/M TLK LINU HRB 5'S</t>
+  </si>
+  <si>
+    <t>20059240</t>
+  </si>
+  <si>
+    <t>ANTANGIN JUNIOR 5'S</t>
+  </si>
+  <si>
+    <t>20041621</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG 5X15ML</t>
+  </si>
+  <si>
+    <t>20114432</t>
+  </si>
+  <si>
+    <t>ANTANGIN HTBTSDA 5'S</t>
+  </si>
+  <si>
+    <t>20054969</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNGR/M 5X15</t>
+  </si>
+  <si>
+    <t>20143712</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNIGHT BOX</t>
+  </si>
+  <si>
+    <t>20093959</t>
+  </si>
+  <si>
+    <t>BEJO JAHE MERAH 6X15</t>
+  </si>
+  <si>
+    <t>20137415</t>
+  </si>
+  <si>
+    <t>MXGRP GRGES JLM 6S</t>
+  </si>
+  <si>
+    <t>20124231</t>
+  </si>
+  <si>
+    <t>MADU TJ MSK ANGIN140</t>
+  </si>
+  <si>
+    <t>20088783</t>
+  </si>
+  <si>
+    <t>MADU TJ PNS DLM 150</t>
+  </si>
+  <si>
+    <t>10003799</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS BOX 6'S</t>
+  </si>
+  <si>
+    <t>20039339</t>
+  </si>
+  <si>
+    <t>SILADEX O/B EXP 60</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20143398</t>
+  </si>
+  <si>
+    <t>ACTF SYRUP PILEK 25</t>
+  </si>
+  <si>
+    <t>20138372</t>
+  </si>
+  <si>
+    <t>KOMIX OBH 6X7ML</t>
+  </si>
+  <si>
+    <t>20092712</t>
+  </si>
+  <si>
+    <t>KOMIX HERBAL 4X15ML</t>
+  </si>
+  <si>
+    <t>10008599</t>
+  </si>
+  <si>
+    <t>OBH/C ANAK STRW 60ML</t>
+  </si>
+  <si>
+    <t>10023206</t>
+  </si>
+  <si>
+    <t>TERMOREX PLUS 60 ML</t>
+  </si>
+  <si>
+    <t>10006565</t>
+  </si>
+  <si>
+    <t>TEMPRA T/PNS ANGR 60</t>
+  </si>
+  <si>
+    <t>10000548</t>
+  </si>
+  <si>
+    <t>CAP LANG NORIT (40)</t>
+  </si>
+  <si>
+    <t>10038823</t>
+  </si>
+  <si>
+    <t>COMBANTRIN JRK 10ML</t>
+  </si>
+  <si>
+    <t>20021454</t>
+  </si>
+  <si>
+    <t>MYLANTA MAAG MINT 50</t>
+  </si>
+  <si>
+    <t>20052643</t>
+  </si>
+  <si>
+    <t>PROMAG HRBAL BOX 6'S</t>
+  </si>
+  <si>
+    <t>20057840</t>
+  </si>
+  <si>
+    <t>POLYSILANE BTL 100</t>
+  </si>
+  <si>
+    <t>20021214</t>
+  </si>
+  <si>
+    <t>VGTA HERBAL ANGR 6'S</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20107145</t>
+  </si>
+  <si>
+    <t>DULCOLAX 10'S</t>
+  </si>
+  <si>
+    <t>20002523</t>
+  </si>
+  <si>
+    <t>ROHTO OBT MATA COL 7</t>
+  </si>
+  <si>
+    <t>20105059</t>
+  </si>
+  <si>
+    <t>ROHTO V-EXTRA 7ML</t>
+  </si>
+  <si>
+    <t>10000149</t>
+  </si>
+  <si>
+    <t>INSTO REG. 7.5 ML</t>
+  </si>
+  <si>
+    <t>10015684</t>
+  </si>
+  <si>
+    <t>INSTO FRY EYES 7.5</t>
+  </si>
+  <si>
+    <t>20122751</t>
+  </si>
+  <si>
+    <t>INSTO COOL 7.5ML</t>
+  </si>
+  <si>
+    <t>20017270</t>
+  </si>
+  <si>
+    <t>VICKS F44 ANK STRW54</t>
+  </si>
+  <si>
+    <t>20120782</t>
+  </si>
+  <si>
+    <t>VICKS JAHE MADU 56ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000144</t>
+  </si>
+  <si>
+    <t>VICKS F44 DWSA 54ML</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20128049</t>
+  </si>
+  <si>
+    <t>VICKS INHALER TWIN</t>
+  </si>
+  <si>
+    <t>10000159</t>
+  </si>
+  <si>
+    <t>VICKS INHALER</t>
+  </si>
+  <si>
+    <t>20137940</t>
+  </si>
+  <si>
+    <t>VICKS BABY BALM 20G</t>
+  </si>
+  <si>
+    <t>20034842</t>
+  </si>
+  <si>
+    <t>VICKS VAPORUB POT 25</t>
+  </si>
+  <si>
+    <t>10020195</t>
+  </si>
+  <si>
+    <t>VICKS VAPORUB 50G</t>
+  </si>
+  <si>
+    <t>20143018</t>
+  </si>
+  <si>
+    <t>VCKS VPRB EXSTRG 25G</t>
+  </si>
+  <si>
+    <t>10000289</t>
+  </si>
+  <si>
+    <t>OBH.C PLUS MNTHL 100</t>
+  </si>
+  <si>
+    <t>10037392</t>
+  </si>
+  <si>
+    <t>OBH.C BDHK MNTHL 100</t>
+  </si>
+  <si>
+    <t>20131299</t>
+  </si>
+  <si>
+    <t>OBH COMBI HERBAL60ML</t>
+  </si>
+  <si>
+    <t>10002978</t>
+  </si>
+  <si>
+    <t>LASERIN O/BATUK 110M</t>
+  </si>
+  <si>
+    <t>20006531</t>
+  </si>
+  <si>
+    <t>WOODS O/B LIQ EXP 60</t>
+  </si>
+  <si>
+    <t>20129489</t>
+  </si>
+  <si>
+    <t>WOODS O/B LIQ NTRL60</t>
+  </si>
+  <si>
+    <t>20124758</t>
+  </si>
+  <si>
+    <t>OB/HRBL HBTSAUDA 60</t>
+  </si>
+  <si>
+    <t>20011850</t>
+  </si>
+  <si>
+    <t>OB HERBAL OBT BTK 60</t>
+  </si>
+  <si>
+    <t>20139611</t>
+  </si>
+  <si>
+    <t>FCARE STRONG 15+5ML</t>
+  </si>
+  <si>
+    <t>20040719</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK/A STRG10</t>
+  </si>
+  <si>
+    <t>20034536</t>
+  </si>
+  <si>
+    <t>FRESH/C MNYK ANGIN10</t>
+  </si>
+  <si>
+    <t>20037203</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK ANG LV10</t>
+  </si>
+  <si>
+    <t>20131218</t>
+  </si>
+  <si>
+    <t>FRS.CR SMASH IN+R/ON</t>
+  </si>
+  <si>
+    <t>20139612</t>
+  </si>
+  <si>
+    <t>FCARE SMASH FRUITY</t>
+  </si>
+  <si>
+    <t>20141438</t>
+  </si>
+  <si>
+    <t>FCARE SMASH SAKURA</t>
+  </si>
+  <si>
+    <t>20135134</t>
+  </si>
+  <si>
+    <t>FRS.CR IN+R/ON MTCHA</t>
+  </si>
+  <si>
+    <t>20141439</t>
+  </si>
+  <si>
+    <t>FCARE VPBLM SAKURA</t>
+  </si>
+  <si>
+    <t>20139593</t>
+  </si>
+  <si>
+    <t>FCARE VPOBALM MATCHA</t>
+  </si>
+  <si>
+    <t>20045178</t>
+  </si>
+  <si>
+    <t>SAFE/C MNYK ANGIN 10</t>
+  </si>
+  <si>
+    <t>20102037</t>
+  </si>
+  <si>
+    <t>SAFE/C MYK AGN STR10</t>
+  </si>
+  <si>
+    <t>20134253</t>
+  </si>
+  <si>
+    <t>SO FRSH HOT 2X10ML</t>
+  </si>
+  <si>
+    <t>20134254</t>
+  </si>
+  <si>
+    <t>SO FRSH EUCLYP2X10ML</t>
+  </si>
+  <si>
+    <t>20141329</t>
+  </si>
+  <si>
+    <t>SO FRSH CTRUS 2X10ML</t>
+  </si>
+  <si>
+    <t>20091326</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S ECALYPT10</t>
+  </si>
+  <si>
+    <t>20122013</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S CITRUS 10</t>
+  </si>
+  <si>
+    <t>20141330</t>
+  </si>
+  <si>
+    <t>PLOSSA DUAL SRGHAEYO</t>
+  </si>
+  <si>
+    <t>10000097</t>
+  </si>
+  <si>
+    <t>C/KAPAK MNYK ANGIN10</t>
+  </si>
+  <si>
+    <t>20054022</t>
+  </si>
+  <si>
+    <t>TAWON 912 O/GSK 50ML</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>20019446</t>
@@ -208,463 +658,13 @@
     <t>C/LANG MINYAK GPU 60</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20054951</t>
-  </si>
-  <si>
-    <t>S/M TOLAK/A ANAK 5'S</t>
-  </si>
-  <si>
-    <t>20034577</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN+MDU 5'S</t>
-  </si>
-  <si>
-    <t>20122907</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN FLU 5'S</t>
-  </si>
-  <si>
-    <t>20064502</t>
-  </si>
-  <si>
-    <t>S/M TLK ANGIN BG 5'S</t>
-  </si>
-  <si>
-    <t>20064503</t>
-  </si>
-  <si>
-    <t>S/M TLK LINU HRB 5'S</t>
-  </si>
-  <si>
-    <t>20059240</t>
-  </si>
-  <si>
-    <t>ANTANGIN JUNIOR 5'S</t>
-  </si>
-  <si>
-    <t>20041621</t>
-  </si>
-  <si>
-    <t>ANTANGIN JRG 5X15ML</t>
-  </si>
-  <si>
-    <t>20114432</t>
-  </si>
-  <si>
-    <t>ANTANGIN HTBTSDA 5'S</t>
-  </si>
-  <si>
-    <t>20054969</t>
-  </si>
-  <si>
-    <t>ANTANGIN GNGR/M 5X15</t>
-  </si>
-  <si>
-    <t>20093959</t>
-  </si>
-  <si>
-    <t>BEJO JAHE MERAH 6X15</t>
-  </si>
-  <si>
-    <t>20137415</t>
-  </si>
-  <si>
-    <t>MXGRP GRGES JLM 6S</t>
-  </si>
-  <si>
-    <t>20124231</t>
-  </si>
-  <si>
-    <t>MADU TJ MSK ANGIN140</t>
-  </si>
-  <si>
-    <t>20088783</t>
-  </si>
-  <si>
-    <t>MADU TJ PNS DLM 150</t>
-  </si>
-  <si>
-    <t>10003799</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS BOX 6'S</t>
-  </si>
-  <si>
-    <t>20139960</t>
-  </si>
-  <si>
-    <t>EJ SPORT ORANGE 2S</t>
-  </si>
-  <si>
-    <t>20039339</t>
-  </si>
-  <si>
-    <t>SILADEX O/B EXP 60</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20143398</t>
-  </si>
-  <si>
-    <t>ACTF SYRUP PILEK 25</t>
-  </si>
-  <si>
-    <t>20138372</t>
-  </si>
-  <si>
-    <t>KOMIX OBH 6X7ML</t>
-  </si>
-  <si>
-    <t>20092712</t>
-  </si>
-  <si>
-    <t>KOMIX HERBAL 4X15ML</t>
-  </si>
-  <si>
-    <t>10008599</t>
-  </si>
-  <si>
-    <t>OBH/C ANAK STRW 60ML</t>
-  </si>
-  <si>
-    <t>10023206</t>
-  </si>
-  <si>
-    <t>TERMOREX PLUS 60 ML</t>
-  </si>
-  <si>
-    <t>10006565</t>
-  </si>
-  <si>
-    <t>TEMPRA T/PNS ANGR 60</t>
-  </si>
-  <si>
-    <t>10000548</t>
-  </si>
-  <si>
-    <t>CAP LANG NORIT (40)</t>
-  </si>
-  <si>
-    <t>10038823</t>
-  </si>
-  <si>
-    <t>COMBANTRIN JRK 10ML</t>
-  </si>
-  <si>
-    <t>20021454</t>
-  </si>
-  <si>
-    <t>MYLANTA MAAG MINT 50</t>
-  </si>
-  <si>
-    <t>20052643</t>
-  </si>
-  <si>
-    <t>PROMAG HRBAL BOX 6'S</t>
-  </si>
-  <si>
-    <t>20057840</t>
-  </si>
-  <si>
-    <t>POLYSILANE BTL 100</t>
-  </si>
-  <si>
-    <t>20021214</t>
-  </si>
-  <si>
-    <t>VGTA HERBAL ANGR 6'S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20107145</t>
-  </si>
-  <si>
-    <t>DULCOLAX 10'S</t>
-  </si>
-  <si>
-    <t>20002523</t>
-  </si>
-  <si>
-    <t>ROHTO OBT MATA COL 7</t>
-  </si>
-  <si>
-    <t>20105059</t>
-  </si>
-  <si>
-    <t>ROHTO V-EXTRA 7ML</t>
-  </si>
-  <si>
-    <t>10000149</t>
-  </si>
-  <si>
-    <t>INSTO REG. 7.5 ML</t>
-  </si>
-  <si>
-    <t>10015684</t>
-  </si>
-  <si>
-    <t>INSTO FRY EYES 7.5</t>
-  </si>
-  <si>
-    <t>20122751</t>
-  </si>
-  <si>
-    <t>INSTO COOL 7.5ML</t>
-  </si>
-  <si>
-    <t>20017270</t>
-  </si>
-  <si>
-    <t>VICKS F44 ANK STRW54</t>
-  </si>
-  <si>
-    <t>20120782</t>
-  </si>
-  <si>
-    <t>VICKS JAHE MADU 56ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000144</t>
-  </si>
-  <si>
-    <t>VICKS F44 DWSA 54ML</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20128049</t>
-  </si>
-  <si>
-    <t>VICKS INHALER TWIN</t>
-  </si>
-  <si>
-    <t>10000159</t>
-  </si>
-  <si>
-    <t>VICKS INHALER</t>
-  </si>
-  <si>
-    <t>20137940</t>
-  </si>
-  <si>
-    <t>VICKS BABY BALM 20G</t>
-  </si>
-  <si>
-    <t>20034842</t>
-  </si>
-  <si>
-    <t>VICKS VAPORUB POT 25</t>
-  </si>
-  <si>
-    <t>10020195</t>
-  </si>
-  <si>
-    <t>VICKS VAPORUB 50G</t>
-  </si>
-  <si>
-    <t>20143018</t>
-  </si>
-  <si>
-    <t>VCKS VPRB EXSTRG 25G</t>
-  </si>
-  <si>
-    <t>10000289</t>
-  </si>
-  <si>
-    <t>OBH.C PLUS MNTHL 100</t>
-  </si>
-  <si>
-    <t>10037392</t>
-  </si>
-  <si>
-    <t>OBH.C BDHK MNTHL 100</t>
-  </si>
-  <si>
-    <t>20131299</t>
-  </si>
-  <si>
-    <t>OBH COMBI HERBAL60ML</t>
-  </si>
-  <si>
-    <t>10002978</t>
-  </si>
-  <si>
-    <t>LASERIN O/BATUK 110M</t>
-  </si>
-  <si>
-    <t>20006531</t>
-  </si>
-  <si>
-    <t>WOODS O/B LIQ EXP 60</t>
-  </si>
-  <si>
-    <t>20129489</t>
-  </si>
-  <si>
-    <t>WOODS O/B LIQ NTRL60</t>
-  </si>
-  <si>
-    <t>20124758</t>
-  </si>
-  <si>
-    <t>OB/HRBL HBTSAUDA 60</t>
-  </si>
-  <si>
-    <t>20011850</t>
-  </si>
-  <si>
-    <t>OB HERBAL OBT BTK 60</t>
-  </si>
-  <si>
-    <t>20139611</t>
-  </si>
-  <si>
-    <t>FCARE STRONG 15+5ML</t>
-  </si>
-  <si>
-    <t>20040719</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK/A STRG10</t>
-  </si>
-  <si>
-    <t>20034536</t>
-  </si>
-  <si>
-    <t>FRESH/C MNYK ANGIN10</t>
-  </si>
-  <si>
-    <t>20037203</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK ANG LV10</t>
-  </si>
-  <si>
-    <t>20131218</t>
-  </si>
-  <si>
-    <t>FRS.CR SMASH IN+R/ON</t>
-  </si>
-  <si>
-    <t>20139612</t>
-  </si>
-  <si>
-    <t>FCARE SMASH FRUITY</t>
-  </si>
-  <si>
-    <t>20141438</t>
-  </si>
-  <si>
-    <t>FCARE SMASH SAKURA</t>
-  </si>
-  <si>
-    <t>20135134</t>
-  </si>
-  <si>
-    <t>FRS.CR IN+R/ON MTCHA</t>
-  </si>
-  <si>
-    <t>20141439</t>
-  </si>
-  <si>
-    <t>FCARE VPBLM SAKURA</t>
-  </si>
-  <si>
-    <t>20139593</t>
-  </si>
-  <si>
-    <t>FCARE VPOBALM MATCHA</t>
-  </si>
-  <si>
-    <t>20045178</t>
-  </si>
-  <si>
-    <t>SAFE/C MNYK ANGIN 10</t>
-  </si>
-  <si>
-    <t>20102037</t>
-  </si>
-  <si>
-    <t>SAFE/C MYK AGN STR10</t>
-  </si>
-  <si>
-    <t>20134253</t>
-  </si>
-  <si>
-    <t>SO FRSH HOT 2X10ML</t>
-  </si>
-  <si>
-    <t>20134254</t>
-  </si>
-  <si>
-    <t>SO FRSH EUCLYP2X10ML</t>
-  </si>
-  <si>
-    <t>20141329</t>
-  </si>
-  <si>
-    <t>SO FRSH CTRUS 2X10ML</t>
-  </si>
-  <si>
-    <t>20091326</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S ECALYPT10</t>
-  </si>
-  <si>
-    <t>20122013</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S CITRUS 10</t>
-  </si>
-  <si>
-    <t>20141330</t>
-  </si>
-  <si>
-    <t>PLOSSA DUAL SRGHAEYO</t>
-  </si>
-  <si>
-    <t>10000097</t>
-  </si>
-  <si>
-    <t>C/KAPAK MNYK ANGIN10</t>
-  </si>
-  <si>
-    <t>20054022</t>
-  </si>
-  <si>
-    <t>TAWON 912 O/GSK 50ML</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>10000553</t>
   </si>
   <si>
     <t>BETADINE SOLUTION 30</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20137313</t>
-  </si>
-  <si>
-    <t>HANSPLST ANTSP 40ML</t>
   </si>
   <si>
     <t>22</t>
@@ -1760,7 +1760,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1800,15 +1800,15 @@
         <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1817,10 +1817,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1840,7 +1840,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1860,7 +1860,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1880,15 +1880,15 @@
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1897,10 +1897,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,15 +1920,15 @@
         <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1937,10 +1937,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1960,7 +1960,7 @@
         <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2197,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2220,7 +2220,7 @@
         <v>36</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2260,7 +2260,7 @@
         <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,10 +2277,10 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
@@ -2560,7 +2560,7 @@
         <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>123</v>
@@ -2617,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
@@ -2877,7 +2877,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>123</v>
@@ -2977,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>12</v>
@@ -3217,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3297,7 +3297,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>123</v>
@@ -3337,7 +3337,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>123</v>
@@ -3460,7 +3460,7 @@
         <v>215</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3480,7 +3480,7 @@
         <v>218</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,7 +3520,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,7 +4060,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4120,7 +4120,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4140,7 +4140,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -4337,7 +4337,7 @@
         <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>12</v>
@@ -4357,7 +4357,7 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>16</v>
@@ -4377,7 +4377,7 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4397,7 +4397,7 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>20</v>
@@ -4637,7 +4637,7 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>123</v>
@@ -4657,7 +4657,7 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>12</v>
@@ -4717,7 +4717,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>123</v>
@@ -4737,7 +4737,7 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>12</v>
@@ -4820,7 +4820,7 @@
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,7 +4900,7 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,7 +4920,7 @@
         <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>29</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4977,10 +4977,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>42</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,7 +5057,7 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5237,7 +5237,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="402">
   <si>
     <t/>
   </si>
@@ -1105,7 +1105,7 @@
     <t>10000425</t>
   </si>
   <si>
-    <t>C/LANG KAYU PUTIH 60</t>
+    <t>C.LANG KYU PTH 60 ML</t>
   </si>
   <si>
     <t>20079757</t>
@@ -1129,13 +1129,10 @@
     <t>20141441</t>
   </si>
   <si>
-    <t>C.LANG MK.BAYI LVD60</t>
+    <t>C.LANG BAYI LVD 60 G</t>
   </si>
   <si>
     <t>20141440</t>
-  </si>
-  <si>
-    <t>C.LANG MK BAYI CHM60</t>
   </si>
   <si>
     <t>10037405</t>
@@ -5008,7 +5005,7 @@
         <v>373</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5025,10 +5022,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5045,10 +5042,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5065,10 +5062,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5085,10 +5082,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5105,10 +5102,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5125,10 +5122,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5145,10 +5142,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5165,10 +5162,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5185,10 +5182,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5205,10 +5202,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5225,10 +5222,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5245,10 +5242,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5265,10 +5262,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5285,10 +5282,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>

--- a/MED01S.xlsx
+++ b/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
   <si>
     <t/>
   </si>
@@ -1133,6 +1133,9 @@
   </si>
   <si>
     <t>20141440</t>
+  </si>
+  <si>
+    <t>C/L KY PTH CHAMILE60</t>
   </si>
   <si>
     <t>10037405</t>
@@ -5005,7 +5008,7 @@
         <v>373</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5022,10 +5025,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5042,10 +5045,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5062,10 +5065,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5082,10 +5085,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5102,10 +5105,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5122,10 +5125,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5142,10 +5145,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5162,10 +5165,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5182,10 +5185,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5202,10 +5205,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5222,10 +5225,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5242,10 +5245,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5262,10 +5265,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5282,10 +5285,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
